--- a/artfynd/A 45691-2023 artfynd.xlsx
+++ b/artfynd/A 45691-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45691-2023 artfynd.xlsx
+++ b/artfynd/A 45691-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73359679</v>
+        <v>73359678</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754467.8202439087</v>
+        <v>754469</v>
       </c>
       <c r="R2" t="n">
-        <v>7141720.024792798</v>
+        <v>7141720</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73359678</v>
+        <v>73359679</v>
       </c>
       <c r="B3" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754469.120499314</v>
+        <v>754468</v>
       </c>
       <c r="R3" t="n">
-        <v>7141720.132763759</v>
+        <v>7141720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73359677</v>
+        <v>73359676</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754469.120499314</v>
+        <v>754469</v>
       </c>
       <c r="R4" t="n">
-        <v>7141720.132763759</v>
+        <v>7141720</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73359676</v>
+        <v>73359677</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754469.120499314</v>
+        <v>754469</v>
       </c>
       <c r="R5" t="n">
-        <v>7141720.132763759</v>
+        <v>7141720</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2017-10-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,12 +1066,7 @@
         <v>86442965</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754570.0804613987</v>
+        <v>754570</v>
       </c>
       <c r="R6" t="n">
-        <v>7141755.105126675</v>
+        <v>7141755</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,19 +1136,9 @@
           <t>2020-06-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-06-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45691-2023 artfynd.xlsx
+++ b/artfynd/A 45691-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73359678</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73359679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73359676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73359677</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86442965</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>